--- a/General Oceans modell.xlsx
+++ b/General Oceans modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F6BEFE-B506-1142-8104-4CC3D8EC091B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE9EA2F-CE67-B14F-B139-2F5FD3A4076D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25180" yWindow="500" windowWidth="26020" windowHeight="26700" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25380" yWindow="500" windowWidth="25060" windowHeight="26500" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -857,7 +857,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0\ %"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1010,12 +1010,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1522,7 +1516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1757,12 +1751,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3092,7 +3085,7 @@
       <c r="D6" s="38"/>
       <c r="T6" s="13">
         <f>Modell!B12</f>
-        <v>-1.7962586712531414</v>
+        <v>-1.7280387777096413</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3108,7 +3101,7 @@
       <c r="D7" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="T7" s="135">
+      <c r="T7" s="134">
         <f>Modell!U60/Modell!U53</f>
         <v>0.73234451915961529</v>
       </c>
@@ -3330,12 +3323,12 @@
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="134" t="s">
+      <c r="A29" s="135" t="s">
         <v>231</v>
       </c>
-      <c r="B29" s="134"/>
-      <c r="C29" s="134"/>
-      <c r="D29" s="134"/>
+      <c r="B29" s="135"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="135"/>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3639,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>44</v>
@@ -3804,7 +3797,7 @@
       </c>
       <c r="B6" s="9">
         <f>B4*B5</f>
-        <v>4229.3967320000002</v>
+        <v>3556.5381609999999</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>46</v>
@@ -3841,43 +3834,43 @@
         <v>-459.06</v>
       </c>
       <c r="AF6" s="20">
-        <f>AF4*-0.31</f>
-        <v>-444.55835200000007</v>
-      </c>
-      <c r="AG6" s="17">
-        <f>AG4*-0.31</f>
-        <v>-511.24210480000005</v>
-      </c>
-      <c r="AH6" s="17">
-        <f>AH4*-0.31</f>
-        <v>-603.26568366399999</v>
+        <f>AF4*-0.3</f>
+        <v>-430.21776000000006</v>
+      </c>
+      <c r="AG6" s="136">
+        <f t="shared" ref="AG6:AH6" si="2">AG4*-0.3</f>
+        <v>-494.75042400000001</v>
+      </c>
+      <c r="AH6" s="136">
+        <f t="shared" si="2"/>
+        <v>-583.80550031999996</v>
       </c>
       <c r="AI6" s="17">
         <f>AI4*-0.3</f>
         <v>-688.89049037760003</v>
       </c>
       <c r="AJ6" s="17">
-        <f t="shared" ref="AJ6:AO6" si="2">AJ4*-0.3</f>
+        <f t="shared" ref="AJ6:AO6" si="3">AJ4*-0.3</f>
         <v>-812.89077864556793</v>
       </c>
       <c r="AK6" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-934.8243954424031</v>
       </c>
       <c r="AL6" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1047.0033228954915</v>
       </c>
       <c r="AM6" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1151.7036551850408</v>
       </c>
       <c r="AN6" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1266.8740207035448</v>
       </c>
       <c r="AO6" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1393.5614227738995</v>
       </c>
     </row>
@@ -3893,11 +3886,11 @@
         <v>47</v>
       </c>
       <c r="P7" s="17">
-        <f t="shared" ref="P7:Q7" si="3">SUM(P4:P6)</f>
+        <f t="shared" ref="P7:Q7" si="4">SUM(P4:P6)</f>
         <v>214.25699999999998</v>
       </c>
       <c r="Q7" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>218.29600000000005</v>
       </c>
       <c r="T7" s="17">
@@ -3910,67 +3903,67 @@
       </c>
       <c r="X7" s="18"/>
       <c r="Z7" s="17">
-        <f t="shared" ref="Z7:AO7" si="4">SUM(Z4:Z6)</f>
+        <f t="shared" ref="Z7:AO7" si="5">SUM(Z4:Z6)</f>
         <v>237.14799999999997</v>
       </c>
       <c r="AA7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>262.50100000000003</v>
       </c>
       <c r="AB7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>445.27699999999993</v>
       </c>
       <c r="AC7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>568.99199999999996</v>
       </c>
       <c r="AD7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>640.80600000000004</v>
       </c>
       <c r="AE7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>844.80200000000013</v>
       </c>
       <c r="AF7" s="20">
         <f>SUM(AF4:AF6)</f>
-        <v>989.50084800000013</v>
+        <v>1003.8414400000001</v>
       </c>
       <c r="AG7" s="17">
-        <f t="shared" si="4"/>
-        <v>1137.9259752</v>
+        <f t="shared" si="5"/>
+        <v>1154.4176560000001</v>
       </c>
       <c r="AH7" s="17">
-        <f t="shared" si="4"/>
-        <v>1342.7526507359999</v>
+        <f t="shared" si="5"/>
+        <v>1362.21283408</v>
       </c>
       <c r="AI7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1607.4111442143999</v>
       </c>
       <c r="AJ7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1896.745150172992</v>
       </c>
       <c r="AK7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2181.2569226989408</v>
       </c>
       <c r="AL7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2443.0077534228139</v>
       </c>
       <c r="AM7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2687.3085287650956</v>
       </c>
       <c r="AN7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2956.0393816416049</v>
       </c>
       <c r="AO7" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3251.6433198057657</v>
       </c>
     </row>
@@ -4020,40 +4013,40 @@
         <v>-496.10067999999995</v>
       </c>
       <c r="AG8" s="17">
-        <f>AF8*1.15</f>
-        <v>-570.51578199999994</v>
+        <f>AF8*1.14</f>
+        <v>-565.55477519999988</v>
       </c>
       <c r="AH8" s="17">
         <f>AG8*1.17</f>
-        <v>-667.50346493999984</v>
+        <v>-661.69908698399979</v>
       </c>
       <c r="AI8" s="17">
-        <f t="shared" ref="AI8" si="5">AH8*1.18</f>
-        <v>-787.6540886291998</v>
+        <f t="shared" ref="AI8" si="6">AH8*1.18</f>
+        <v>-780.80492264111967</v>
       </c>
       <c r="AJ8" s="17">
         <f>AI8*1.17</f>
-        <v>-921.55528369616377</v>
+        <v>-913.54175949010994</v>
       </c>
       <c r="AK8" s="17">
         <f>AJ8*1.15</f>
-        <v>-1059.7885762505882</v>
+        <v>-1050.5730234136263</v>
       </c>
       <c r="AL8" s="17">
         <f>AK8*1.12</f>
-        <v>-1186.9632054006588</v>
+        <v>-1176.6417862232615</v>
       </c>
       <c r="AM8" s="17">
         <f>AL8*1.1</f>
-        <v>-1305.6595259407247</v>
+        <v>-1294.3059648455878</v>
       </c>
       <c r="AN8" s="17">
-        <f t="shared" ref="AN8:AO8" si="6">AM8*1.1</f>
-        <v>-1436.2254785347973</v>
+        <f t="shared" ref="AN8:AO8" si="7">AM8*1.1</f>
+        <v>-1423.7365613301467</v>
       </c>
       <c r="AO8" s="17">
-        <f t="shared" si="6"/>
-        <v>-1579.848026388277</v>
+        <f t="shared" si="7"/>
+        <v>-1566.1102174631615</v>
       </c>
     </row>
     <row r="9" spans="1:41" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -4062,7 +4055,7 @@
       </c>
       <c r="B9" s="10">
         <f>B6-B7+B8</f>
-        <v>3683.5787319999999</v>
+        <v>3010.7201610000002</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>49</v>
@@ -4098,44 +4091,44 @@
         <v>-64.817999999999998</v>
       </c>
       <c r="AF9" s="20">
-        <f t="shared" ref="AF9:AF11" si="7">AE9*1.16</f>
-        <v>-75.188879999999997</v>
+        <f t="shared" ref="AF9:AF11" si="8">AE9*1.15</f>
+        <v>-74.540699999999987</v>
       </c>
       <c r="AG9" s="17">
-        <f t="shared" ref="AG9:AG10" si="8">AF9*1.15</f>
-        <v>-86.467211999999989</v>
+        <f t="shared" ref="AG9:AG11" si="9">AF9*1.14</f>
+        <v>-84.976397999999975</v>
       </c>
       <c r="AH9" s="17">
-        <f t="shared" ref="AH9:AH11" si="9">AG9*1.18</f>
-        <v>-102.03131015999998</v>
+        <f t="shared" ref="AH9:AH11" si="10">AG9*1.18</f>
+        <v>-100.27214963999997</v>
       </c>
       <c r="AI9" s="17">
-        <f t="shared" ref="AI9:AJ9" si="10">AH9*1.18</f>
-        <v>-120.39694598879997</v>
+        <f t="shared" ref="AI9:AJ9" si="11">AH9*1.18</f>
+        <v>-118.32113657519996</v>
       </c>
       <c r="AJ9" s="17">
-        <f t="shared" si="10"/>
-        <v>-142.06839626678396</v>
+        <f t="shared" si="11"/>
+        <v>-139.61894115873594</v>
       </c>
       <c r="AK9" s="17">
-        <f t="shared" ref="AK9:AK10" si="11">AJ9*1.15</f>
-        <v>-163.37865570680154</v>
+        <f t="shared" ref="AK9:AK10" si="12">AJ9*1.15</f>
+        <v>-160.5617823325463</v>
       </c>
       <c r="AL9" s="17">
-        <f t="shared" ref="AL9:AL10" si="12">AK9*1.12</f>
-        <v>-182.98409439161773</v>
+        <f t="shared" ref="AL9:AL10" si="13">AK9*1.12</f>
+        <v>-179.82919621245188</v>
       </c>
       <c r="AM9" s="17">
-        <f t="shared" ref="AM9:AO9" si="13">AL9*1.1</f>
-        <v>-201.28250383077952</v>
+        <f t="shared" ref="AM9:AO9" si="14">AL9*1.1</f>
+        <v>-197.81211583369708</v>
       </c>
       <c r="AN9" s="17">
-        <f t="shared" si="13"/>
-        <v>-221.4107542138575</v>
+        <f t="shared" si="14"/>
+        <v>-217.5933274170668</v>
       </c>
       <c r="AO9" s="17">
-        <f t="shared" si="13"/>
-        <v>-243.55182963524328</v>
+        <f t="shared" si="14"/>
+        <v>-239.35266015877349</v>
       </c>
     </row>
     <row r="10" spans="1:41" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -4175,43 +4168,44 @@
         <v>-158.63200000000001</v>
       </c>
       <c r="AF10" s="20">
-        <v>-180</v>
+        <f t="shared" si="8"/>
+        <v>-182.42679999999999</v>
       </c>
       <c r="AG10" s="17">
-        <f t="shared" si="8"/>
-        <v>-206.99999999999997</v>
+        <f t="shared" si="9"/>
+        <v>-207.96655199999998</v>
       </c>
       <c r="AH10" s="17">
-        <f t="shared" si="9"/>
-        <v>-244.25999999999996</v>
+        <f t="shared" si="10"/>
+        <v>-245.40053135999997</v>
       </c>
       <c r="AI10" s="17">
-        <f t="shared" ref="AI10:AJ10" si="14">AH10*1.18</f>
-        <v>-288.22679999999997</v>
+        <f t="shared" ref="AI10:AJ10" si="15">AH10*1.18</f>
+        <v>-289.57262700479993</v>
       </c>
       <c r="AJ10" s="17">
-        <f t="shared" si="14"/>
-        <v>-340.10762399999993</v>
+        <f t="shared" si="15"/>
+        <v>-341.69569986566387</v>
       </c>
       <c r="AK10" s="17">
-        <f t="shared" si="11"/>
-        <v>-391.12376759999989</v>
+        <f t="shared" si="12"/>
+        <v>-392.95005484551342</v>
       </c>
       <c r="AL10" s="17">
-        <f t="shared" si="12"/>
-        <v>-438.05861971199994</v>
+        <f t="shared" si="13"/>
+        <v>-440.10406142697508</v>
       </c>
       <c r="AM10" s="17">
-        <f t="shared" ref="AM10:AO10" si="15">AL10*1.1</f>
-        <v>-481.86448168319998</v>
+        <f t="shared" ref="AM10:AO10" si="16">AL10*1.1</f>
+        <v>-484.11446756967263</v>
       </c>
       <c r="AN10" s="17">
-        <f t="shared" si="15"/>
-        <v>-530.05092985151998</v>
+        <f t="shared" si="16"/>
+        <v>-532.52591432663996</v>
       </c>
       <c r="AO10" s="17">
-        <f t="shared" si="15"/>
-        <v>-583.05602283667201</v>
+        <f t="shared" si="16"/>
+        <v>-585.77850575930404</v>
       </c>
     </row>
     <row r="11" spans="1:41" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -4251,16 +4245,16 @@
         <v>-8.2210000000000001</v>
       </c>
       <c r="AF11" s="20">
-        <f t="shared" si="7"/>
-        <v>-9.5363600000000002</v>
+        <f t="shared" si="8"/>
+        <v>-9.4541499999999985</v>
       </c>
       <c r="AG11" s="17">
-        <f t="shared" ref="AG11" si="16">AF11*1.175</f>
-        <v>-11.205223</v>
+        <f t="shared" si="9"/>
+        <v>-10.777730999999998</v>
       </c>
       <c r="AH11" s="17">
-        <f t="shared" si="9"/>
-        <v>-13.222163139999999</v>
+        <f t="shared" si="10"/>
+        <v>-12.717722579999997</v>
       </c>
       <c r="AI11" s="17">
         <v>0</v>
@@ -4290,7 +4284,7 @@
       </c>
       <c r="B12" s="12">
         <f>(B8-B7)/AF27</f>
-        <v>-1.7962586712531414</v>
+        <v>-1.7280387777096413</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>52</v>
@@ -4393,43 +4387,43 @@
       </c>
       <c r="AF12" s="55">
         <f t="shared" si="18"/>
-        <v>228.67492800000019</v>
+        <v>241.31911000000025</v>
       </c>
       <c r="AG12" s="18">
         <f t="shared" si="18"/>
-        <v>262.73775820000009</v>
+        <v>285.14219980000024</v>
       </c>
       <c r="AH12" s="18">
         <f t="shared" si="18"/>
-        <v>315.73571249600002</v>
+        <v>342.12334351600032</v>
       </c>
       <c r="AI12" s="18">
         <f t="shared" si="18"/>
-        <v>411.13330959640012</v>
+        <v>418.71245799328034</v>
       </c>
       <c r="AJ12" s="18">
         <f t="shared" si="18"/>
-        <v>493.01384621004428</v>
+        <v>501.8887496584822</v>
       </c>
       <c r="AK12" s="18">
         <f t="shared" si="18"/>
-        <v>566.96592314155123</v>
+        <v>577.17206210725476</v>
       </c>
       <c r="AL12" s="18">
         <f t="shared" si="18"/>
-        <v>635.00183391853761</v>
+        <v>646.43270956012543</v>
       </c>
       <c r="AM12" s="18">
         <f t="shared" si="18"/>
-        <v>698.50201731039147</v>
+        <v>711.07598051613809</v>
       </c>
       <c r="AN12" s="18">
         <f t="shared" si="18"/>
-        <v>768.3522190414302</v>
+        <v>782.1835785677514</v>
       </c>
       <c r="AO12" s="18">
         <f t="shared" si="18"/>
-        <v>845.18744094557326</v>
+        <v>860.40193642452675</v>
       </c>
     </row>
     <row r="13" spans="1:41" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -4757,43 +4751,43 @@
       </c>
       <c r="AF16" s="20">
         <f t="shared" si="23"/>
-        <v>233.05392800000016</v>
+        <v>245.69811000000027</v>
       </c>
       <c r="AG16" s="17">
         <f t="shared" si="23"/>
-        <v>270.08053820000009</v>
+        <v>292.48497980000025</v>
       </c>
       <c r="AH16" s="17">
         <f t="shared" si="23"/>
-        <v>326.46494449600004</v>
+        <v>352.85257551600034</v>
       </c>
       <c r="AI16" s="17">
         <f t="shared" si="23"/>
-        <v>425.72024749640019</v>
+        <v>433.2993958932804</v>
       </c>
       <c r="AJ16" s="17">
         <f t="shared" si="23"/>
-        <v>511.98349973504435</v>
+        <v>520.85840318348221</v>
       </c>
       <c r="AK16" s="17">
         <f t="shared" si="23"/>
-        <v>590.90276494580121</v>
+        <v>601.10890391150474</v>
       </c>
       <c r="AL16" s="17">
         <f t="shared" si="23"/>
-        <v>664.55609397630019</v>
+        <v>675.98696961788801</v>
       </c>
       <c r="AM16" s="17">
         <f t="shared" si="23"/>
-        <v>734.3966241506721</v>
+        <v>746.97058735641872</v>
       </c>
       <c r="AN16" s="17">
         <f t="shared" si="23"/>
-        <v>811.39045338131803</v>
+        <v>825.22181290763922</v>
       </c>
       <c r="AO16" s="17">
         <f t="shared" si="23"/>
-        <v>896.26137387580764</v>
+        <v>911.47586935476113</v>
       </c>
     </row>
     <row r="17" spans="1:241" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -4833,43 +4827,43 @@
       </c>
       <c r="AF17" s="20">
         <f>AF16*-0.22</f>
-        <v>-51.271864160000035</v>
+        <v>-54.05358420000006</v>
       </c>
       <c r="AG17" s="17">
         <f t="shared" ref="AG17:AO17" si="24">AG16*-0.22</f>
-        <v>-59.41771840400002</v>
+        <v>-64.346695556000057</v>
       </c>
       <c r="AH17" s="17">
         <f t="shared" si="24"/>
-        <v>-71.822287789120011</v>
+        <v>-77.627566613520074</v>
       </c>
       <c r="AI17" s="17">
         <f t="shared" si="24"/>
-        <v>-93.658454449208037</v>
+        <v>-95.325867096521691</v>
       </c>
       <c r="AJ17" s="17">
         <f t="shared" si="24"/>
-        <v>-112.63636994170976</v>
+        <v>-114.58884870036609</v>
       </c>
       <c r="AK17" s="17">
         <f t="shared" si="24"/>
-        <v>-129.99860828807627</v>
+        <v>-132.24395886053105</v>
       </c>
       <c r="AL17" s="17">
         <f t="shared" si="24"/>
-        <v>-146.20234067478603</v>
+        <v>-148.71713331593537</v>
       </c>
       <c r="AM17" s="17">
         <f t="shared" si="24"/>
-        <v>-161.56725731314785</v>
+        <v>-164.33352921841211</v>
       </c>
       <c r="AN17" s="17">
         <f t="shared" si="24"/>
-        <v>-178.50589974388996</v>
+        <v>-181.54879883968064</v>
       </c>
       <c r="AO17" s="17">
         <f t="shared" si="24"/>
-        <v>-197.17750225267767</v>
+        <v>-200.52469125804745</v>
       </c>
     </row>
     <row r="18" spans="1:241" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4976,843 +4970,843 @@
       </c>
       <c r="AF18" s="55">
         <f t="shared" si="27"/>
-        <v>181.78206384000012</v>
+        <v>191.64452580000022</v>
       </c>
       <c r="AG18" s="18">
         <f t="shared" si="27"/>
-        <v>210.66281979600006</v>
+        <v>228.1382842440002</v>
       </c>
       <c r="AH18" s="18">
         <f t="shared" si="27"/>
-        <v>254.64265670688002</v>
+        <v>275.22500890248028</v>
       </c>
       <c r="AI18" s="18">
         <f t="shared" si="27"/>
-        <v>332.06179304719217</v>
+        <v>337.97352879675873</v>
       </c>
       <c r="AJ18" s="18">
         <f t="shared" si="27"/>
-        <v>399.3471297933346</v>
+        <v>406.26955448311611</v>
       </c>
       <c r="AK18" s="18">
         <f t="shared" si="27"/>
-        <v>460.90415665772491</v>
+        <v>468.86494505097369</v>
       </c>
       <c r="AL18" s="18">
         <f t="shared" si="27"/>
-        <v>518.35375330151419</v>
+        <v>527.26983630195264</v>
       </c>
       <c r="AM18" s="18">
         <f t="shared" si="27"/>
-        <v>572.82936683752428</v>
+        <v>582.63705813800664</v>
       </c>
       <c r="AN18" s="18">
         <f t="shared" si="27"/>
-        <v>632.8845536374281</v>
+        <v>643.67301406795855</v>
       </c>
       <c r="AO18" s="18">
         <f t="shared" si="27"/>
-        <v>699.08387162312999</v>
+        <v>710.95117809671365</v>
       </c>
       <c r="AP18" s="18">
         <f>AO18*(1+$AR$22)</f>
-        <v>692.09303290689866</v>
+        <v>703.84166631574647</v>
       </c>
       <c r="AQ18" s="18">
         <f t="shared" ref="AQ18:DB18" si="28">AP18*(1+$AR$22)</f>
-        <v>685.17210257782972</v>
+        <v>696.80324965258899</v>
       </c>
       <c r="AR18" s="18">
         <f t="shared" si="28"/>
-        <v>678.32038155205146</v>
+        <v>689.83521715606309</v>
       </c>
       <c r="AS18" s="18">
         <f t="shared" si="28"/>
-        <v>671.53717773653091</v>
+        <v>682.93686498450245</v>
       </c>
       <c r="AT18" s="18">
         <f t="shared" si="28"/>
-        <v>664.82180595916554</v>
+        <v>676.10749633465741</v>
       </c>
       <c r="AU18" s="18">
         <f t="shared" si="28"/>
-        <v>658.17358789957393</v>
+        <v>669.34642137131084</v>
       </c>
       <c r="AV18" s="18">
         <f t="shared" si="28"/>
-        <v>651.59185202057813</v>
+        <v>662.65295715759771</v>
       </c>
       <c r="AW18" s="18">
         <f t="shared" si="28"/>
-        <v>645.07593350037234</v>
+        <v>656.02642758602178</v>
       </c>
       <c r="AX18" s="18">
         <f t="shared" si="28"/>
-        <v>638.62517416536866</v>
+        <v>649.46616331016151</v>
       </c>
       <c r="AY18" s="18">
         <f t="shared" si="28"/>
-        <v>632.23892242371494</v>
+        <v>642.9715016770599</v>
       </c>
       <c r="AZ18" s="18">
         <f t="shared" si="28"/>
-        <v>625.91653319947784</v>
+        <v>636.54178666028929</v>
       </c>
       <c r="BA18" s="18">
         <f t="shared" si="28"/>
-        <v>619.657367867483</v>
+        <v>630.17636879368638</v>
       </c>
       <c r="BB18" s="18">
         <f t="shared" si="28"/>
-        <v>613.46079418880822</v>
+        <v>623.87460510574954</v>
       </c>
       <c r="BC18" s="18">
         <f t="shared" si="28"/>
-        <v>607.32618624692009</v>
+        <v>617.63585905469199</v>
       </c>
       <c r="BD18" s="18">
         <f t="shared" si="28"/>
-        <v>601.25292438445092</v>
+        <v>611.45950046414509</v>
       </c>
       <c r="BE18" s="18">
         <f t="shared" si="28"/>
-        <v>595.24039514060644</v>
+        <v>605.34490545950359</v>
       </c>
       <c r="BF18" s="18">
         <f t="shared" si="28"/>
-        <v>589.2879911892004</v>
+        <v>599.29145640490856</v>
       </c>
       <c r="BG18" s="18">
         <f t="shared" si="28"/>
-        <v>583.39511127730839</v>
+        <v>593.29854184085946</v>
       </c>
       <c r="BH18" s="18">
         <f t="shared" si="28"/>
-        <v>577.56116016453529</v>
+        <v>587.36555642245082</v>
       </c>
       <c r="BI18" s="18">
         <f t="shared" si="28"/>
-        <v>571.78554856288997</v>
+        <v>581.49190085822636</v>
       </c>
       <c r="BJ18" s="18">
         <f t="shared" si="28"/>
-        <v>566.06769307726108</v>
+        <v>575.67698184964411</v>
       </c>
       <c r="BK18" s="18">
         <f t="shared" si="28"/>
-        <v>560.40701614648844</v>
+        <v>569.92021203114768</v>
       </c>
       <c r="BL18" s="18">
         <f t="shared" si="28"/>
-        <v>554.8029459850236</v>
+        <v>564.22100991083619</v>
       </c>
       <c r="BM18" s="18">
         <f t="shared" si="28"/>
-        <v>549.25491652517337</v>
+        <v>558.57879981172778</v>
       </c>
       <c r="BN18" s="18">
         <f t="shared" si="28"/>
-        <v>543.76236735992165</v>
+        <v>552.99301181361045</v>
       </c>
       <c r="BO18" s="18">
         <f t="shared" si="28"/>
-        <v>538.32474368632245</v>
+        <v>547.46308169547433</v>
       </c>
       <c r="BP18" s="18">
         <f t="shared" si="28"/>
-        <v>532.94149624945919</v>
+        <v>541.98845087851953</v>
       </c>
       <c r="BQ18" s="18">
         <f t="shared" si="28"/>
-        <v>527.61208128696455</v>
+        <v>536.5685663697343</v>
       </c>
       <c r="BR18" s="18">
         <f t="shared" si="28"/>
-        <v>522.33596047409492</v>
+        <v>531.20288070603692</v>
       </c>
       <c r="BS18" s="18">
         <f t="shared" si="28"/>
-        <v>517.11260086935397</v>
+        <v>525.89085189897651</v>
       </c>
       <c r="BT18" s="18">
         <f t="shared" si="28"/>
-        <v>511.94147486066043</v>
+        <v>520.63194337998675</v>
       </c>
       <c r="BU18" s="18">
         <f t="shared" si="28"/>
-        <v>506.8220601120538</v>
+        <v>515.42562394618687</v>
       </c>
       <c r="BV18" s="18">
         <f t="shared" si="28"/>
-        <v>501.75383951093329</v>
+        <v>510.27136770672502</v>
       </c>
       <c r="BW18" s="18">
         <f t="shared" si="28"/>
-        <v>496.73630111582395</v>
+        <v>505.16865402965777</v>
       </c>
       <c r="BX18" s="18">
         <f t="shared" si="28"/>
-        <v>491.76893810466572</v>
+        <v>500.11696748936117</v>
       </c>
       <c r="BY18" s="18">
         <f t="shared" si="28"/>
-        <v>486.85124872361905</v>
+        <v>495.11579781446756</v>
       </c>
       <c r="BZ18" s="18">
         <f t="shared" si="28"/>
-        <v>481.98273623638283</v>
+        <v>490.16463983632286</v>
       </c>
       <c r="CA18" s="18">
         <f t="shared" si="28"/>
-        <v>477.16290887401902</v>
+        <v>485.26299343795961</v>
       </c>
       <c r="CB18" s="18">
         <f t="shared" si="28"/>
-        <v>472.39127978527881</v>
+        <v>480.41036350358002</v>
       </c>
       <c r="CC18" s="18">
         <f t="shared" si="28"/>
-        <v>467.66736698742602</v>
+        <v>475.60625986854421</v>
       </c>
       <c r="CD18" s="18">
         <f t="shared" si="28"/>
-        <v>462.99069331755175</v>
+        <v>470.85019726985877</v>
       </c>
       <c r="CE18" s="18">
         <f t="shared" si="28"/>
-        <v>458.36078638437624</v>
+        <v>466.1416952971602</v>
       </c>
       <c r="CF18" s="18">
         <f t="shared" si="28"/>
-        <v>453.77717852053246</v>
+        <v>461.4802783441886</v>
       </c>
       <c r="CG18" s="18">
         <f t="shared" si="28"/>
-        <v>449.23940673532712</v>
+        <v>456.86547556074669</v>
       </c>
       <c r="CH18" s="18">
         <f t="shared" si="28"/>
-        <v>444.74701266797382</v>
+        <v>452.29682080513919</v>
       </c>
       <c r="CI18" s="18">
         <f t="shared" si="28"/>
-        <v>440.2995425412941</v>
+        <v>447.7738525970878</v>
       </c>
       <c r="CJ18" s="18">
         <f t="shared" si="28"/>
-        <v>435.89654711588116</v>
+        <v>443.2961140711169</v>
       </c>
       <c r="CK18" s="18">
         <f t="shared" si="28"/>
-        <v>431.53758164472237</v>
+        <v>438.8631529304057</v>
       </c>
       <c r="CL18" s="18">
         <f t="shared" si="28"/>
-        <v>427.22220582827515</v>
+        <v>434.47452140110164</v>
       </c>
       <c r="CM18" s="18">
         <f t="shared" si="28"/>
-        <v>422.9499837699924</v>
+        <v>430.12977618709061</v>
       </c>
       <c r="CN18" s="18">
         <f t="shared" si="28"/>
-        <v>418.7204839322925</v>
+        <v>425.82847842521971</v>
       </c>
       <c r="CO18" s="18">
         <f t="shared" si="28"/>
-        <v>414.53327909296956</v>
+        <v>421.57019364096749</v>
       </c>
       <c r="CP18" s="18">
         <f t="shared" si="28"/>
-        <v>410.38794630203989</v>
+        <v>417.3544917045578</v>
       </c>
       <c r="CQ18" s="18">
         <f t="shared" si="28"/>
-        <v>406.28406683901949</v>
+        <v>413.1809467875122</v>
       </c>
       <c r="CR18" s="18">
         <f t="shared" si="28"/>
-        <v>402.22122617062928</v>
+        <v>409.04913731963705</v>
       </c>
       <c r="CS18" s="18">
         <f t="shared" si="28"/>
-        <v>398.19901390892301</v>
+        <v>404.9586459464407</v>
       </c>
       <c r="CT18" s="18">
         <f t="shared" si="28"/>
-        <v>394.21702376983376</v>
+        <v>400.90905948697628</v>
       </c>
       <c r="CU18" s="18">
         <f t="shared" si="28"/>
-        <v>390.27485353213541</v>
+        <v>396.89996889210653</v>
       </c>
       <c r="CV18" s="18">
         <f t="shared" si="28"/>
-        <v>386.37210499681407</v>
+        <v>392.93096920318544</v>
       </c>
       <c r="CW18" s="18">
         <f t="shared" si="28"/>
-        <v>382.50838394684592</v>
+        <v>389.0016595111536</v>
       </c>
       <c r="CX18" s="18">
         <f t="shared" si="28"/>
-        <v>378.68330010737748</v>
+        <v>385.11164291604206</v>
       </c>
       <c r="CY18" s="18">
         <f t="shared" si="28"/>
-        <v>374.8964671063037</v>
+        <v>381.26052648688164</v>
       </c>
       <c r="CZ18" s="18">
         <f t="shared" si="28"/>
-        <v>371.14750243524065</v>
+        <v>377.44792122201284</v>
       </c>
       <c r="DA18" s="18">
         <f t="shared" si="28"/>
-        <v>367.43602741088824</v>
+        <v>373.67344200979272</v>
       </c>
       <c r="DB18" s="18">
         <f t="shared" si="28"/>
-        <v>363.76166713677935</v>
+        <v>369.93670758969478</v>
       </c>
       <c r="DC18" s="18">
         <f t="shared" ref="DC18:FN18" si="29">DB18*(1+$AR$22)</f>
-        <v>360.12405046541153</v>
+        <v>366.23734051379785</v>
       </c>
       <c r="DD18" s="18">
         <f t="shared" si="29"/>
-        <v>356.5228099607574</v>
+        <v>362.57496710865985</v>
       </c>
       <c r="DE18" s="18">
         <f t="shared" si="29"/>
-        <v>352.95758186114983</v>
+        <v>358.94921743757322</v>
       </c>
       <c r="DF18" s="18">
         <f t="shared" si="29"/>
-        <v>349.42800604253836</v>
+        <v>355.3597252631975</v>
       </c>
       <c r="DG18" s="18">
         <f t="shared" si="29"/>
-        <v>345.93372598211295</v>
+        <v>351.80612801056554</v>
       </c>
       <c r="DH18" s="18">
         <f t="shared" si="29"/>
-        <v>342.47438872229179</v>
+        <v>348.28806673045989</v>
       </c>
       <c r="DI18" s="18">
         <f t="shared" si="29"/>
-        <v>339.04964483506888</v>
+        <v>344.8051860631553</v>
       </c>
       <c r="DJ18" s="18">
         <f t="shared" si="29"/>
-        <v>335.65914838671819</v>
+        <v>341.35713420252375</v>
       </c>
       <c r="DK18" s="18">
         <f t="shared" si="29"/>
-        <v>332.30255690285099</v>
+        <v>337.9435628604985</v>
       </c>
       <c r="DL18" s="18">
         <f t="shared" si="29"/>
-        <v>328.97953133382248</v>
+        <v>334.56412723189351</v>
       </c>
       <c r="DM18" s="18">
         <f t="shared" si="29"/>
-        <v>325.68973602048425</v>
+        <v>331.21848595957459</v>
       </c>
       <c r="DN18" s="18">
         <f t="shared" si="29"/>
-        <v>322.4328386602794</v>
+        <v>327.90630109997886</v>
       </c>
       <c r="DO18" s="18">
         <f t="shared" si="29"/>
-        <v>319.20851027367661</v>
+        <v>324.62723808897908</v>
       </c>
       <c r="DP18" s="18">
         <f t="shared" si="29"/>
-        <v>316.01642517093984</v>
+        <v>321.38096570808926</v>
       </c>
       <c r="DQ18" s="18">
         <f t="shared" si="29"/>
-        <v>312.85626091923046</v>
+        <v>318.16715605100836</v>
       </c>
       <c r="DR18" s="18">
         <f t="shared" si="29"/>
-        <v>309.72769831003814</v>
+        <v>314.98548449049827</v>
       </c>
       <c r="DS18" s="18">
         <f t="shared" si="29"/>
-        <v>306.63042132693778</v>
+        <v>311.83562964559326</v>
       </c>
       <c r="DT18" s="18">
         <f t="shared" si="29"/>
-        <v>303.56411711366837</v>
+        <v>308.71727334913732</v>
       </c>
       <c r="DU18" s="18">
         <f t="shared" si="29"/>
-        <v>300.52847594253171</v>
+        <v>305.63010061564592</v>
       </c>
       <c r="DV18" s="18">
         <f t="shared" si="29"/>
-        <v>297.52319118310641</v>
+        <v>302.57379960948947</v>
       </c>
       <c r="DW18" s="18">
         <f t="shared" si="29"/>
-        <v>294.54795927127532</v>
+        <v>299.54806161339457</v>
       </c>
       <c r="DX18" s="18">
         <f t="shared" si="29"/>
-        <v>291.60247967856259</v>
+        <v>296.55258099726063</v>
       </c>
       <c r="DY18" s="18">
         <f t="shared" si="29"/>
-        <v>288.68645488177697</v>
+        <v>293.587055187288</v>
       </c>
       <c r="DZ18" s="18">
         <f t="shared" si="29"/>
-        <v>285.79959033295921</v>
+        <v>290.65118463541512</v>
       </c>
       <c r="EA18" s="18">
         <f t="shared" si="29"/>
-        <v>282.94159442962962</v>
+        <v>287.74467278906098</v>
       </c>
       <c r="EB18" s="18">
         <f t="shared" si="29"/>
-        <v>280.11217848533335</v>
+        <v>284.86722606117036</v>
       </c>
       <c r="EC18" s="18">
         <f t="shared" si="29"/>
-        <v>277.31105670048004</v>
+        <v>282.01855380055866</v>
       </c>
       <c r="ED18" s="18">
         <f t="shared" si="29"/>
-        <v>274.53794613347526</v>
+        <v>279.19836826255306</v>
       </c>
       <c r="EE18" s="18">
         <f t="shared" si="29"/>
-        <v>271.79256667214048</v>
+        <v>276.40638457992753</v>
       </c>
       <c r="EF18" s="18">
         <f t="shared" si="29"/>
-        <v>269.0746410054191</v>
+        <v>273.64232073412825</v>
       </c>
       <c r="EG18" s="18">
         <f t="shared" si="29"/>
-        <v>266.38389459536489</v>
+        <v>270.90589752678699</v>
       </c>
       <c r="EH18" s="18">
         <f t="shared" si="29"/>
-        <v>263.72005564941122</v>
+        <v>268.19683855151914</v>
       </c>
       <c r="EI18" s="18">
         <f t="shared" si="29"/>
-        <v>261.0828550929171</v>
+        <v>265.51487016600396</v>
       </c>
       <c r="EJ18" s="18">
         <f t="shared" si="29"/>
-        <v>258.47202654198793</v>
+        <v>262.85972146434392</v>
       </c>
       <c r="EK18" s="18">
         <f t="shared" si="29"/>
-        <v>255.88730627656804</v>
+        <v>260.23112424970049</v>
       </c>
       <c r="EL18" s="18">
         <f t="shared" si="29"/>
-        <v>253.32843321380236</v>
+        <v>257.62881300720346</v>
       </c>
       <c r="EM18" s="18">
         <f t="shared" si="29"/>
-        <v>250.79514888166432</v>
+        <v>255.05252487713142</v>
       </c>
       <c r="EN18" s="18">
         <f t="shared" si="29"/>
-        <v>248.28719739284767</v>
+        <v>252.5019996283601</v>
       </c>
       <c r="EO18" s="18">
         <f t="shared" si="29"/>
-        <v>245.80432541891921</v>
+        <v>249.97697963207651</v>
       </c>
       <c r="EP18" s="18">
         <f t="shared" si="29"/>
-        <v>243.34628216473001</v>
+        <v>247.47720983575573</v>
       </c>
       <c r="EQ18" s="18">
         <f t="shared" si="29"/>
-        <v>240.9128193430827</v>
+        <v>245.00243773739817</v>
       </c>
       <c r="ER18" s="18">
         <f t="shared" si="29"/>
-        <v>238.50369114965187</v>
+        <v>242.55241336002419</v>
       </c>
       <c r="ES18" s="18">
         <f t="shared" si="29"/>
-        <v>236.11865423815536</v>
+        <v>240.12688922642394</v>
       </c>
       <c r="ET18" s="18">
         <f t="shared" si="29"/>
-        <v>233.75746769577381</v>
+        <v>237.72562033415969</v>
       </c>
       <c r="EU18" s="18">
         <f t="shared" si="29"/>
-        <v>231.41989301881608</v>
+        <v>235.34836413081808</v>
       </c>
       <c r="EV18" s="18">
         <f t="shared" si="29"/>
-        <v>229.10569408862793</v>
+        <v>232.99488048950991</v>
       </c>
       <c r="EW18" s="18">
         <f t="shared" si="29"/>
-        <v>226.81463714774165</v>
+        <v>230.6649316846148</v>
       </c>
       <c r="EX18" s="18">
         <f t="shared" si="29"/>
-        <v>224.54649077626422</v>
+        <v>228.35828236776865</v>
       </c>
       <c r="EY18" s="18">
         <f t="shared" si="29"/>
-        <v>222.30102586850157</v>
+        <v>226.07469954409098</v>
       </c>
       <c r="EZ18" s="18">
         <f t="shared" si="29"/>
-        <v>220.07801560981656</v>
+        <v>223.81395254865006</v>
       </c>
       <c r="FA18" s="18">
         <f t="shared" si="29"/>
-        <v>217.87723545371838</v>
+        <v>221.57581302316356</v>
       </c>
       <c r="FB18" s="18">
         <f t="shared" si="29"/>
-        <v>215.6984630991812</v>
+        <v>219.36005489293191</v>
       </c>
       <c r="FC18" s="18">
         <f t="shared" si="29"/>
-        <v>213.54147846818938</v>
+        <v>217.1664543440026</v>
       </c>
       <c r="FD18" s="18">
         <f t="shared" si="29"/>
-        <v>211.40606368350748</v>
+        <v>214.99478980056259</v>
       </c>
       <c r="FE18" s="18">
         <f t="shared" si="29"/>
-        <v>209.29200304667242</v>
+        <v>212.84484190255696</v>
       </c>
       <c r="FF18" s="18">
         <f t="shared" si="29"/>
-        <v>207.19908301620569</v>
+        <v>210.71639348353139</v>
       </c>
       <c r="FG18" s="18">
         <f t="shared" si="29"/>
-        <v>205.12709218604363</v>
+        <v>208.60922954869608</v>
       </c>
       <c r="FH18" s="18">
         <f t="shared" si="29"/>
-        <v>203.07582126418319</v>
+        <v>206.52313725320911</v>
       </c>
       <c r="FI18" s="18">
         <f t="shared" si="29"/>
-        <v>201.04506305154135</v>
+        <v>204.45790588067703</v>
       </c>
       <c r="FJ18" s="18">
         <f t="shared" si="29"/>
-        <v>199.03461242102594</v>
+        <v>202.41332682187027</v>
       </c>
       <c r="FK18" s="18">
         <f t="shared" si="29"/>
-        <v>197.04426629681569</v>
+        <v>200.38919355365158</v>
       </c>
       <c r="FL18" s="18">
         <f t="shared" si="29"/>
-        <v>195.07382363384752</v>
+        <v>198.38530161811505</v>
       </c>
       <c r="FM18" s="18">
         <f t="shared" si="29"/>
-        <v>193.12308539750904</v>
+        <v>196.40144860193391</v>
       </c>
       <c r="FN18" s="18">
         <f t="shared" si="29"/>
-        <v>191.19185454353396</v>
+        <v>194.43743411591456</v>
       </c>
       <c r="FO18" s="18">
         <f t="shared" ref="FO18:HZ18" si="30">FN18*(1+$AR$22)</f>
-        <v>189.27993599809864</v>
+        <v>192.49305977475541</v>
       </c>
       <c r="FP18" s="18">
         <f t="shared" si="30"/>
-        <v>187.38713663811765</v>
+        <v>190.56812917700785</v>
       </c>
       <c r="FQ18" s="18">
         <f t="shared" si="30"/>
-        <v>185.51326527173649</v>
+        <v>188.66244788523775</v>
       </c>
       <c r="FR18" s="18">
         <f t="shared" si="30"/>
-        <v>183.65813261901911</v>
+        <v>186.77582340638537</v>
       </c>
       <c r="FS18" s="18">
         <f t="shared" si="30"/>
-        <v>181.82155129282893</v>
+        <v>184.90806517232153</v>
       </c>
       <c r="FT18" s="18">
         <f t="shared" si="30"/>
-        <v>180.00333577990062</v>
+        <v>183.0589845205983</v>
       </c>
       <c r="FU18" s="18">
         <f t="shared" si="30"/>
-        <v>178.20330242210161</v>
+        <v>181.22839467539231</v>
       </c>
       <c r="FV18" s="18">
         <f t="shared" si="30"/>
-        <v>176.42126939788059</v>
+        <v>179.41611072863839</v>
       </c>
       <c r="FW18" s="18">
         <f t="shared" si="30"/>
-        <v>174.65705670390179</v>
+        <v>177.621949621352</v>
       </c>
       <c r="FX18" s="18">
         <f t="shared" si="30"/>
-        <v>172.91048613686277</v>
+        <v>175.84573012513849</v>
       </c>
       <c r="FY18" s="18">
         <f t="shared" si="30"/>
-        <v>171.18138127549415</v>
+        <v>174.0872728238871</v>
       </c>
       <c r="FZ18" s="18">
         <f t="shared" si="30"/>
-        <v>169.46956746273921</v>
+        <v>172.34640009564822</v>
       </c>
       <c r="GA18" s="18">
         <f t="shared" si="30"/>
-        <v>167.77487178811182</v>
+        <v>170.62293609469174</v>
       </c>
       <c r="GB18" s="18">
         <f t="shared" si="30"/>
-        <v>166.09712307023071</v>
+        <v>168.91670673374483</v>
       </c>
       <c r="GC18" s="18">
         <f t="shared" si="30"/>
-        <v>164.43615183952841</v>
+        <v>167.22753966640738</v>
       </c>
       <c r="GD18" s="18">
         <f t="shared" si="30"/>
-        <v>162.79179032113313</v>
+        <v>165.5552642697433</v>
       </c>
       <c r="GE18" s="18">
         <f t="shared" si="30"/>
-        <v>161.16387241792179</v>
+        <v>163.89971162704586</v>
       </c>
       <c r="GF18" s="18">
         <f t="shared" si="30"/>
-        <v>159.55223369374258</v>
+        <v>162.26071451077539</v>
       </c>
       <c r="GG18" s="18">
         <f t="shared" si="30"/>
-        <v>157.95671135680516</v>
+        <v>160.63810736566762</v>
       </c>
       <c r="GH18" s="18">
         <f t="shared" si="30"/>
-        <v>156.3771442432371</v>
+        <v>159.03172629201094</v>
       </c>
       <c r="GI18" s="18">
         <f t="shared" si="30"/>
-        <v>154.81337280080473</v>
+        <v>157.44140902909083</v>
       </c>
       <c r="GJ18" s="18">
         <f t="shared" si="30"/>
-        <v>153.26523907279667</v>
+        <v>155.86699493879993</v>
       </c>
       <c r="GK18" s="18">
         <f t="shared" si="30"/>
-        <v>151.7325866820687</v>
+        <v>154.30832498941194</v>
       </c>
       <c r="GL18" s="18">
         <f t="shared" si="30"/>
-        <v>150.215260815248</v>
+        <v>152.76524173951782</v>
       </c>
       <c r="GM18" s="18">
         <f t="shared" si="30"/>
-        <v>148.71310820709553</v>
+        <v>151.23758932212263</v>
       </c>
       <c r="GN18" s="18">
         <f t="shared" si="30"/>
-        <v>147.22597712502457</v>
+        <v>149.72521342890141</v>
       </c>
       <c r="GO18" s="18">
         <f t="shared" si="30"/>
-        <v>145.75371735377433</v>
+        <v>148.22796129461238</v>
       </c>
       <c r="GP18" s="18">
         <f t="shared" si="30"/>
-        <v>144.29618018023658</v>
+        <v>146.74568168166627</v>
       </c>
       <c r="GQ18" s="18">
         <f t="shared" si="30"/>
-        <v>142.85321837843421</v>
+        <v>145.27822486484962</v>
       </c>
       <c r="GR18" s="18">
         <f t="shared" si="30"/>
-        <v>141.42468619464987</v>
+        <v>143.82544261620112</v>
       </c>
       <c r="GS18" s="18">
         <f t="shared" si="30"/>
-        <v>140.01043933270336</v>
+        <v>142.3871881900391</v>
       </c>
       <c r="GT18" s="18">
         <f t="shared" si="30"/>
-        <v>138.61033493937632</v>
+        <v>140.9633163081387</v>
       </c>
       <c r="GU18" s="18">
         <f t="shared" si="30"/>
-        <v>137.22423158998254</v>
+        <v>139.55368314505731</v>
       </c>
       <c r="GV18" s="18">
         <f t="shared" si="30"/>
-        <v>135.85198927408271</v>
+        <v>138.15814631360672</v>
       </c>
       <c r="GW18" s="18">
         <f t="shared" si="30"/>
-        <v>134.4934693813419</v>
+        <v>136.77656485047066</v>
       </c>
       <c r="GX18" s="18">
         <f t="shared" si="30"/>
-        <v>133.14853468752847</v>
+        <v>135.40879920196596</v>
       </c>
       <c r="GY18" s="18">
         <f t="shared" si="30"/>
-        <v>131.81704934065317</v>
+        <v>134.0547112099463</v>
       </c>
       <c r="GZ18" s="18">
         <f t="shared" si="30"/>
-        <v>130.49887884724663</v>
+        <v>132.71416409784683</v>
       </c>
       <c r="HA18" s="18">
         <f t="shared" si="30"/>
-        <v>129.19389005877417</v>
+        <v>131.38702245686835</v>
       </c>
       <c r="HB18" s="18">
         <f t="shared" si="30"/>
-        <v>127.90195115818644</v>
+        <v>130.07315223229966</v>
       </c>
       <c r="HC18" s="18">
         <f t="shared" si="30"/>
-        <v>126.62293164660457</v>
+        <v>128.77242070997667</v>
       </c>
       <c r="HD18" s="18">
         <f t="shared" si="30"/>
-        <v>125.35670233013852</v>
+        <v>127.4846965028769</v>
       </c>
       <c r="HE18" s="18">
         <f t="shared" si="30"/>
-        <v>124.10313530683713</v>
+        <v>126.20984953784813</v>
       </c>
       <c r="HF18" s="18">
         <f t="shared" si="30"/>
-        <v>122.86210395376875</v>
+        <v>124.94775104246965</v>
       </c>
       <c r="HG18" s="18">
         <f t="shared" si="30"/>
-        <v>121.63348291423107</v>
+        <v>123.69827353204495</v>
       </c>
       <c r="HH18" s="18">
         <f t="shared" si="30"/>
-        <v>120.41714808508875</v>
+        <v>122.4612907967245</v>
       </c>
       <c r="HI18" s="18">
         <f t="shared" si="30"/>
-        <v>119.21297660423787</v>
+        <v>121.23667788875726</v>
       </c>
       <c r="HJ18" s="18">
         <f t="shared" si="30"/>
-        <v>118.02084683819548</v>
+        <v>120.02431110986969</v>
       </c>
       <c r="HK18" s="18">
         <f t="shared" si="30"/>
-        <v>116.84063836981352</v>
+        <v>118.82406799877099</v>
       </c>
       <c r="HL18" s="18">
         <f t="shared" si="30"/>
-        <v>115.67223198611538</v>
+        <v>117.63582731878327</v>
       </c>
       <c r="HM18" s="18">
         <f t="shared" si="30"/>
-        <v>114.51550966625422</v>
+        <v>116.45946904559544</v>
       </c>
       <c r="HN18" s="18">
         <f t="shared" si="30"/>
-        <v>113.37035456959167</v>
+        <v>115.29487435513948</v>
       </c>
       <c r="HO18" s="18">
         <f t="shared" si="30"/>
-        <v>112.23665102389575</v>
+        <v>114.14192561158809</v>
       </c>
       <c r="HP18" s="18">
         <f t="shared" si="30"/>
-        <v>111.11428451365678</v>
+        <v>113.00050635547221</v>
       </c>
       <c r="HQ18" s="18">
         <f t="shared" si="30"/>
-        <v>110.00314166852021</v>
+        <v>111.87050129191749</v>
       </c>
       <c r="HR18" s="18">
         <f t="shared" si="30"/>
-        <v>108.90311025183502</v>
+        <v>110.75179627899831</v>
       </c>
       <c r="HS18" s="18">
         <f t="shared" si="30"/>
-        <v>107.81407914931667</v>
+        <v>109.64427831620833</v>
       </c>
       <c r="HT18" s="18">
         <f t="shared" si="30"/>
-        <v>106.7359383578235</v>
+        <v>108.54783553304624</v>
       </c>
       <c r="HU18" s="18">
         <f t="shared" si="30"/>
-        <v>105.66857897424526</v>
+        <v>107.46235717771577</v>
       </c>
       <c r="HV18" s="18">
         <f t="shared" si="30"/>
-        <v>104.6118931845028</v>
+        <v>106.38773360593862</v>
       </c>
       <c r="HW18" s="18">
         <f t="shared" si="30"/>
-        <v>103.56577425265777</v>
+        <v>105.32385626987923</v>
       </c>
       <c r="HX18" s="18">
         <f t="shared" si="30"/>
-        <v>102.53011651013119</v>
+        <v>104.27061770718043</v>
       </c>
       <c r="HY18" s="18">
         <f t="shared" si="30"/>
-        <v>101.50481534502988</v>
+        <v>103.22791153010863</v>
       </c>
       <c r="HZ18" s="18">
         <f t="shared" si="30"/>
-        <v>100.48976719157959</v>
+        <v>102.19563241480753</v>
       </c>
       <c r="IA18" s="18">
         <f t="shared" ref="IA18:IG18" si="31">HZ18*(1+$AR$22)</f>
-        <v>99.484869519663789</v>
+        <v>101.17367609065946</v>
       </c>
       <c r="IB18" s="18">
         <f t="shared" si="31"/>
-        <v>98.490020824467152</v>
+        <v>100.16193932975285</v>
       </c>
       <c r="IC18" s="18">
         <f t="shared" si="31"/>
-        <v>97.505120616222484</v>
+        <v>99.160319936455323</v>
       </c>
       <c r="ID18" s="18">
         <f t="shared" si="31"/>
-        <v>96.530069410060264</v>
+        <v>98.168716737090776</v>
       </c>
       <c r="IE18" s="18">
         <f t="shared" si="31"/>
-        <v>95.564768715959659</v>
+        <v>97.187029569719869</v>
       </c>
       <c r="IF18" s="18">
         <f t="shared" si="31"/>
-        <v>94.609121028800061</v>
+        <v>96.215159274022668</v>
       </c>
       <c r="IG18" s="18">
         <f t="shared" si="31"/>
-        <v>93.663029818512058</v>
+        <v>95.25300768128244</v>
       </c>
     </row>
     <row r="19" spans="1:241" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -5986,43 +5980,43 @@
       </c>
       <c r="AF20" s="80">
         <f>AF18/AF19</f>
-        <v>0.95448056190742792</v>
+        <v>1.0062652541620889</v>
       </c>
       <c r="AG20" s="26">
         <f t="shared" ref="AG20:AO20" si="36">AG18/AG19</f>
-        <v>1.1061243467280091</v>
+        <v>1.1978825255800312</v>
       </c>
       <c r="AH20" s="26">
         <f t="shared" si="36"/>
-        <v>1.3370486665456209</v>
+        <v>1.44512013781203</v>
       </c>
       <c r="AI20" s="26">
         <f t="shared" si="36"/>
-        <v>1.7435522521883136</v>
+        <v>1.7745929211129496</v>
       </c>
       <c r="AJ20" s="26">
         <f t="shared" si="36"/>
-        <v>2.0968464368231383</v>
+        <v>2.1331939161513525</v>
       </c>
       <c r="AK20" s="26">
         <f t="shared" si="36"/>
-        <v>2.4200630641939691</v>
+        <v>2.4618626654214157</v>
       </c>
       <c r="AL20" s="26">
         <f t="shared" si="36"/>
-        <v>2.7217128646615389</v>
+        <v>2.7685284180362784</v>
       </c>
       <c r="AM20" s="26">
         <f t="shared" si="36"/>
-        <v>3.0077472132640959</v>
+        <v>3.0592443219763092</v>
       </c>
       <c r="AN20" s="26">
         <f t="shared" si="36"/>
-        <v>3.323078149833727</v>
+        <v>3.3797249694171607</v>
       </c>
       <c r="AO20" s="26">
         <f t="shared" si="36"/>
-        <v>3.6706699908224834</v>
+        <v>3.7329814923642615</v>
       </c>
     </row>
     <row r="21" spans="1:241" x14ac:dyDescent="0.25">
@@ -6285,15 +6279,15 @@
       </c>
       <c r="AF23" s="58">
         <f>AF7/AF4</f>
-        <v>0.69000000000000006</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="AG23" s="15">
         <f t="shared" si="42"/>
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="AH23" s="15">
         <f t="shared" si="42"/>
-        <v>0.69</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="AI23" s="15">
         <f t="shared" si="42"/>
@@ -6328,7 +6322,7 @@
       </c>
       <c r="AR23" s="73">
         <f>NPV(AR21,AF18:IG18)</f>
-        <v>6171.6509962398377</v>
+        <v>6308.0379322426288</v>
       </c>
     </row>
     <row r="24" spans="1:241" x14ac:dyDescent="0.25">
@@ -6436,43 +6430,43 @@
       </c>
       <c r="AF24" s="58">
         <f t="shared" si="45"/>
-        <v>0.15945989398485094</v>
+        <v>0.16827695118862612</v>
       </c>
       <c r="AG24" s="15">
         <f t="shared" si="45"/>
-        <v>0.15931533079393584</v>
+        <v>0.17290062987394239</v>
       </c>
       <c r="AH24" s="15">
         <f t="shared" si="45"/>
-        <v>0.16224703894855558</v>
+        <v>0.17580684491417417</v>
       </c>
       <c r="AI24" s="15">
         <f t="shared" si="45"/>
-        <v>0.17904150892156162</v>
+        <v>0.18234209813105667</v>
       </c>
       <c r="AJ24" s="15">
         <f t="shared" si="45"/>
-        <v>0.18194837209182024</v>
+        <v>0.18522368423026958</v>
       </c>
       <c r="AK24" s="15">
         <f t="shared" si="45"/>
-        <v>0.18194837209182035</v>
+        <v>0.18522368423026969</v>
       </c>
       <c r="AL24" s="15">
         <f t="shared" si="45"/>
-        <v>0.18194837209182041</v>
+        <v>0.18522368423026969</v>
       </c>
       <c r="AM24" s="15">
         <f t="shared" si="45"/>
-        <v>0.18194837209182041</v>
+        <v>0.18522368423026969</v>
       </c>
       <c r="AN24" s="15">
         <f t="shared" si="45"/>
-        <v>0.1819483720918203</v>
+        <v>0.18522368423026958</v>
       </c>
       <c r="AO24" s="15">
         <f t="shared" si="45"/>
-        <v>0.1819483720918203</v>
+        <v>0.18522368423026961</v>
       </c>
       <c r="AQ24" s="2" t="s">
         <v>2</v>
@@ -6505,7 +6499,7 @@
       </c>
       <c r="AR25" s="13">
         <f>AR23/AR24</f>
-        <v>32.405402306205509</v>
+        <v>33.12152729985371</v>
       </c>
     </row>
     <row r="26" spans="1:241" x14ac:dyDescent="0.25">
@@ -6535,7 +6529,7 @@
       </c>
       <c r="AR26" s="16">
         <f>(AR25-B4)/B4</f>
-        <v>0.47297283210025043</v>
+        <v>0.79035282701911946</v>
       </c>
     </row>
     <row r="27" spans="1:241" x14ac:dyDescent="0.25">
@@ -6587,43 +6581,43 @@
       </c>
       <c r="AF27" s="20">
         <f>AF12-AF9</f>
-        <v>303.86380800000018</v>
+        <v>315.85981000000027</v>
       </c>
       <c r="AG27" s="17">
         <f t="shared" ref="AG27:AO27" si="46">AG12-AG9</f>
-        <v>349.20497020000005</v>
+        <v>370.1185978000002</v>
       </c>
       <c r="AH27" s="17">
         <f t="shared" si="46"/>
-        <v>417.76702265599999</v>
+        <v>442.39549315600027</v>
       </c>
       <c r="AI27" s="17">
         <f t="shared" si="46"/>
-        <v>531.53025558520005</v>
+        <v>537.03359456848034</v>
       </c>
       <c r="AJ27" s="17">
         <f t="shared" si="46"/>
-        <v>635.08224247682824</v>
+        <v>641.50769081721819</v>
       </c>
       <c r="AK27" s="17">
         <f t="shared" si="46"/>
-        <v>730.34457884835274</v>
+        <v>737.73384443980103</v>
       </c>
       <c r="AL27" s="17">
         <f t="shared" si="46"/>
-        <v>817.98592831015537</v>
+        <v>826.26190577257728</v>
       </c>
       <c r="AM27" s="17">
         <f t="shared" si="46"/>
-        <v>899.78452114117101</v>
+        <v>908.88809634983522</v>
       </c>
       <c r="AN27" s="17">
         <f t="shared" si="46"/>
-        <v>989.76297325528776</v>
+        <v>999.7769059848182</v>
       </c>
       <c r="AO27" s="17">
         <f t="shared" si="46"/>
-        <v>1088.7392705808165</v>
+        <v>1099.7545965833003</v>
       </c>
     </row>
     <row r="28" spans="1:241" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6680,43 +6674,43 @@
       </c>
       <c r="AF28" s="82">
         <f>AF27/AF4</f>
-        <v>0.21189070018866735</v>
+        <v>0.22025576768378896</v>
       </c>
       <c r="AG28" s="21">
         <f t="shared" ref="AG28:AO28" si="48">AG27/AG4</f>
-        <v>0.21174613699775224</v>
+        <v>0.22442745666045161</v>
       </c>
       <c r="AH28" s="21">
         <f t="shared" si="48"/>
-        <v>0.21467784515237195</v>
+        <v>0.22733367170068339</v>
       </c>
       <c r="AI28" s="21">
         <f t="shared" si="48"/>
-        <v>0.231472315125378</v>
+        <v>0.23386892491756592</v>
       </c>
       <c r="AJ28" s="21">
         <f t="shared" si="48"/>
-        <v>0.23437917829563665</v>
+        <v>0.23675051101677883</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="48"/>
-        <v>0.23437917829563673</v>
+        <v>0.23675051101677888</v>
       </c>
       <c r="AL28" s="21">
         <f t="shared" si="48"/>
-        <v>0.23437917829563681</v>
+        <v>0.23675051101677888</v>
       </c>
       <c r="AM28" s="21">
         <f t="shared" si="48"/>
-        <v>0.23437917829563681</v>
+        <v>0.23675051101677891</v>
       </c>
       <c r="AN28" s="21">
         <f t="shared" si="48"/>
-        <v>0.23437917829563673</v>
+        <v>0.2367505110167788</v>
       </c>
       <c r="AO28" s="21">
         <f t="shared" si="48"/>
-        <v>0.2343791782956367</v>
+        <v>0.23675051101677883</v>
       </c>
     </row>
     <row r="29" spans="1:241" x14ac:dyDescent="0.25">
@@ -6908,30 +6902,28 @@
       <c r="AF32" s="82"/>
       <c r="AG32" s="21"/>
     </row>
-    <row r="33" spans="1:33" s="136" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="137"/>
-      <c r="C33" s="136" t="s">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="C33" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="P33" s="136">
+      <c r="P33" s="2">
         <v>325</v>
       </c>
-      <c r="Q33" s="136">
+      <c r="Q33" s="2">
         <v>200</v>
       </c>
-      <c r="R33" s="136">
+      <c r="R33" s="2">
         <v>420</v>
       </c>
-      <c r="S33" s="136">
+      <c r="S33" s="2">
         <v>204</v>
       </c>
-      <c r="T33" s="136">
+      <c r="T33" s="2">
         <v>304</v>
       </c>
-      <c r="U33" s="136">
+      <c r="U33" s="2">
         <v>331</v>
       </c>
-      <c r="AF33" s="137"/>
     </row>
     <row r="34" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
@@ -6976,34 +6968,31 @@
       <c r="AF34" s="82"/>
       <c r="AG34" s="21"/>
     </row>
-    <row r="35" spans="1:33" s="136" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="137"/>
-      <c r="C35" s="136" t="s">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="C35" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="P35" s="136">
+      <c r="P35" s="2">
         <v>573</v>
       </c>
-      <c r="Q35" s="136">
+      <c r="Q35" s="2">
         <v>496</v>
       </c>
-      <c r="R35" s="136">
+      <c r="R35" s="2">
         <v>647</v>
       </c>
-      <c r="S35" s="136">
+      <c r="S35" s="2">
         <v>587</v>
       </c>
-      <c r="T35" s="136">
+      <c r="T35" s="2">
         <v>546</v>
       </c>
-      <c r="U35" s="136">
+      <c r="U35" s="2">
         <v>548</v>
       </c>
-      <c r="AF35" s="137"/>
-    </row>
-    <row r="36" spans="1:33" s="136" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="137"/>
-      <c r="C36" s="136" t="s">
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
         <v>253</v>
       </c>
       <c r="P36" s="13">
@@ -7030,7 +7019,6 @@
         <f>U33/U4</f>
         <v>0.86844956826774478</v>
       </c>
-      <c r="AF36" s="137"/>
     </row>
     <row r="37" spans="1:33" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
@@ -13454,7 +13442,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="133">
         <f>Modell!AF12</f>
-        <v>228.67492800000019</v>
+        <v>241.31911000000025</v>
       </c>
       <c r="D3" s="22">
         <f>SUM(D6:D9)</f>
@@ -13595,7 +13583,10 @@
       <c r="C10" s="85" t="s">
         <v>195</v>
       </c>
-      <c r="D10" s="85"/>
+      <c r="D10" s="85">
+        <f>SUM(D6:D9)</f>
+        <v>225</v>
+      </c>
       <c r="E10" s="85"/>
       <c r="F10" s="86"/>
       <c r="G10" s="87">
@@ -13750,15 +13741,15 @@
       </c>
       <c r="D5" s="74">
         <f>Modell!$B$9/Modell!AF27</f>
-        <v>12.122466167474601</v>
+        <v>9.5318241374234915</v>
       </c>
       <c r="E5" s="74">
         <f>Modell!$B$9/Modell!AG27</f>
-        <v>10.548471660899629</v>
+        <v>8.1344741358468386</v>
       </c>
       <c r="F5" s="74">
         <f>Modell!$B$9/Modell!AH27</f>
-        <v>8.8173037416434674</v>
+        <v>6.8054946480622061</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -13767,15 +13758,15 @@
       </c>
       <c r="D6" s="8">
         <f>Modell!$B$9/Modell!AF12</f>
-        <v>16.108362924684059</v>
+        <v>12.47609508007881</v>
       </c>
       <c r="E6" s="8">
         <f>Modell!$B$9/Modell!AG12</f>
-        <v>14.019982347554333</v>
+        <v>10.558662180174419</v>
       </c>
       <c r="F6" s="74">
         <f>Modell!$B$9/Modell!AH12</f>
-        <v>11.666652159428009</v>
+        <v>8.8001015366529529</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -13784,15 +13775,15 @@
       </c>
       <c r="D7" s="74">
         <f>Modell!$B$4/Modell!AF20</f>
-        <v>23.0491859949828</v>
+        <v>18.384814464656081</v>
       </c>
       <c r="E7" s="74">
         <f>Modell!$B$4/Modell!AG20</f>
-        <v>19.889264769442509</v>
+        <v>15.443918418496043</v>
       </c>
       <c r="F7" s="74">
         <f>Modell!$B$4/Modell!AH20</f>
-        <v>16.454150511094614</v>
+        <v>12.801703827897482</v>
       </c>
     </row>
   </sheetData>
